--- a/business_surveys/038_gasoil_usage_survey--business_surveys.xlsx
+++ b/business_surveys/038_gasoil_usage_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'diesel'}</t>
+          <t>diesel</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Diesel'}</t>
+          <t>Diesel</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'gasoline'}</t>
+          <t>gasoline</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Gasoline'}</t>
+          <t>Gasoline</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'car'}</t>
+          <t>car</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Car'}</t>
+          <t>Car</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'truck'}</t>
+          <t>truck</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Truck'}</t>
+          <t>Truck</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'office'}</t>
+          <t>office</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Office'}</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'home'}</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Home'}</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'night'}</t>
+          <t>night</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Night'}</t>
+          <t>Night</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
